--- a/artfynd/A 18692-2026 artfynd.xlsx
+++ b/artfynd/A 18692-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133816740</v>
+        <v>133816340</v>
       </c>
       <c r="B2" t="n">
         <v>8455</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501353</v>
+        <v>501432</v>
       </c>
       <c r="R2" t="n">
-        <v>6806368</v>
+        <v>6806322</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fl tallar</t>
+          <t>Flera lågor. Sandtallskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133816340</v>
+        <v>133816740</v>
       </c>
       <c r="B3" t="n">
         <v>8455</v>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501432</v>
+        <v>501353</v>
       </c>
       <c r="R3" t="n">
-        <v>6806322</v>
+        <v>6806368</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera lågor. Sandtallskog</t>
+          <t>Fl tallar</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18692-2026 artfynd.xlsx
+++ b/artfynd/A 18692-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133816340</v>
+        <v>133816740</v>
       </c>
       <c r="B2" t="n">
         <v>8455</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501432</v>
+        <v>501353</v>
       </c>
       <c r="R2" t="n">
-        <v>6806322</v>
+        <v>6806368</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera lågor. Sandtallskog</t>
+          <t>Fl tallar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133816740</v>
+        <v>133816340</v>
       </c>
       <c r="B3" t="n">
         <v>8455</v>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501353</v>
+        <v>501432</v>
       </c>
       <c r="R3" t="n">
-        <v>6806368</v>
+        <v>6806322</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fl tallar</t>
+          <t>Flera lågor. Sandtallskog</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18692-2026 artfynd.xlsx
+++ b/artfynd/A 18692-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133816740</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>133816340</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>133816374</v>
       </c>
       <c r="B4" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18692-2026 artfynd.xlsx
+++ b/artfynd/A 18692-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>133816374</v>
       </c>
       <c r="B4" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18692-2026 artfynd.xlsx
+++ b/artfynd/A 18692-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133816740</v>
+        <v>133816340</v>
       </c>
       <c r="B2" t="n">
         <v>8460</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501353</v>
+        <v>501432</v>
       </c>
       <c r="R2" t="n">
-        <v>6806368</v>
+        <v>6806322</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fl tallar</t>
+          <t>Flera lågor. Sandtallskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133816340</v>
+        <v>133816740</v>
       </c>
       <c r="B3" t="n">
         <v>8460</v>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501432</v>
+        <v>501353</v>
       </c>
       <c r="R3" t="n">
-        <v>6806322</v>
+        <v>6806368</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera lågor. Sandtallskog</t>
+          <t>Fl tallar</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18692-2026 artfynd.xlsx
+++ b/artfynd/A 18692-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133816340</v>
+        <v>133816740</v>
       </c>
       <c r="B2" t="n">
         <v>8460</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501432</v>
+        <v>501353</v>
       </c>
       <c r="R2" t="n">
-        <v>6806322</v>
+        <v>6806368</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera lågor. Sandtallskog</t>
+          <t>Fl tallar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133816740</v>
+        <v>133816340</v>
       </c>
       <c r="B3" t="n">
         <v>8460</v>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501353</v>
+        <v>501432</v>
       </c>
       <c r="R3" t="n">
-        <v>6806368</v>
+        <v>6806322</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fl tallar</t>
+          <t>Flera lågor. Sandtallskog</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18692-2026 artfynd.xlsx
+++ b/artfynd/A 18692-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133816740</v>
+        <v>133816374</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>57162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501353</v>
+        <v>501432</v>
       </c>
       <c r="R2" t="n">
-        <v>6806368</v>
+        <v>6806322</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fl tallar</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133816374</v>
+        <v>133816740</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>8460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,27 +915,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501432</v>
+        <v>501353</v>
       </c>
       <c r="R4" t="n">
-        <v>6806322</v>
+        <v>6806368</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fl tallar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18692-2026 artfynd.xlsx
+++ b/artfynd/A 18692-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133816374</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133816340</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,8 +1033,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133816740</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>